--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Ward Pulse</t>
   </si>
   <si>
-    <t xml:space="preserve">Each Ward you control gains 1 HP.</t>
+    <t xml:space="preserve">Each Ward you control gains 1 HP. If you control a Ward, deal 1 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Scales with Ward density. Weak early but synergizes with multi-Ward strategies at higher levels.</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">Burning Hands</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 damage. Place 1 Burn marker on your opponent. (At the start of each of your opponent's turns, each Burn marker on them deals 1 damage. Burns expire at end of round.)</t>
+    <t xml:space="preserve">Deal 1 damage. Place 1 Burn marker on your opponent. (At the start of each of your opponent's turns, each Burn marker on them deals 1 damage; then one Burn marker is removed.)</t>
   </si>
   <si>
     <t xml:space="preserve">First Burn card establishes the keyword. DoT is Evocation's answer to Abjuration's slow defensive game — it ticks while the opponent is busy building Wards.</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">Kindle</t>
   </si>
   <si>
-    <t xml:space="preserve">Place 2 Burn markers on your opponent.</t>
+    <t xml:space="preserve">Place 1 Burn marker on your opponent.</t>
   </si>
   <si>
     <t xml:space="preserve">EVO-007</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">Foretell</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at your opponent's hand.</t>
+    <t xml:space="preserve">Look at your opponent's hand. Deal 1 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Cheap information. Against a reactive Abjuration deck, knowing which counters they hold lets you sequence safely around them.</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">Your opponent puts the top 2 cards of their Resource Deck into their discard pile.</t>
   </si>
   <si>
-    <t xml:space="preserve">Opens the alternate win condition — decking the opponent out. Slow but inevitable against a defensive deck that wants long rounds.</t>
+    <t xml:space="preserve">Accelerates the opponent’s exhaustion clock — every milled card brings their next reshuffle (and its escalating damage) closer.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-021</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">Far Sight</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at the top 3 cards of your opponent's Resource Deck. You may put one of them into their discard pile.</t>
+    <t xml:space="preserve">Look at the top 3 cards of your opponent's Resource Deck. You may put one of them into their discard pile. Deal 1 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Information and light mill in one. Strips an answer off the top before they ever see it.</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">Shuffle your discard pile into your Resource Deck, then draw 2 cards.</t>
   </si>
   <si>
-    <t xml:space="preserve">Refills the whole deck mid-game — anti-deck-out insurance and a huge tempo reset. Against an Abjuration grind, you simply never run out.</t>
+    <t xml:space="preserve">A free reshuffle — resets your deck WITHOUT the exhaustion damage a forced recycle costs, then draws 2. Anti-mill and anti-exhaustion tech.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-029</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">Your opponent shuffles their hand into their Resource Deck, then puts the top 8 cards of their Resource Deck into their discard pile.</t>
   </si>
   <si>
-    <t xml:space="preserve">The deck-out win condition made real. Against an Abjuration deck content to durdle behind Wards, this ends the game from the deck itself.</t>
+    <t xml:space="preserve">The mill haymaker — dumps 8 cards toward the opponent’s next exhaustion tick and scrambles their hand on the way.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-044</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">Shuffle your discard pile into your Resource Deck.</t>
   </si>
   <si>
-    <t xml:space="preserve">Counter — Divination (mill / deck-out)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The anti-deck-out tech — refill so the mill plan can't close. Dead against a fast clock.</t>
+    <t xml:space="preserve">Counter — Divination (mill / exhaustion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-mill / anti-exhaustion tech — a free recycle that dodges the escalating reshuffle damage. Dead against a fast clock.</t>
   </si>
   <si>
     <t xml:space="preserve">GAM-017</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">Counter / Complement — Mill</t>
   </si>
   <si>
-    <t xml:space="preserve">Free mill for any deck — supports a deck-out plan or pressures a fragile combo deck. Modest at 3 cards and one-per-turn.</t>
+    <t xml:space="preserve">Free mill for any deck — pushes the opponent toward their next exhaustion tick, or pressures a fragile combo deck. Modest at 3 cards and one-per-turn.</t>
   </si>
   <si>
     <t xml:space="preserve">GAM-020</t>
@@ -4163,7 +4163,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>241</v>
@@ -4188,7 +4188,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>241</v>
@@ -4294,7 +4294,7 @@
         <v>34</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>241</v>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">M</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw 1 card from your Resource Deck.</t>
+    <t xml:space="preserve">Draw 2 cards from your Resource Deck.</t>
   </si>
   <si>
     <t xml:space="preserve">The school's baseline cantrip and clean reference point: 1 M for 1 card. The consistency engine every Divination deck is built around.</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">Premonition</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw 1 card. If it is a multi-symbol component card, draw an additional card.</t>
+    <t xml:space="preserve">Draw 2 cards. If either is a multi-symbol component card, draw a third.</t>
   </si>
   <si>
     <t xml:space="preserve">Pays off the dual- and tri-component cards Divination leans on to hit off-color costs. A tuned deck turns this into a two-for-one.</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">Foretell</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at your opponent's hand. Deal 1 damage.</t>
+    <t xml:space="preserve">Look at your opponent's hand. Deal 2 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Cheap information. Against a reactive Abjuration deck, knowing which counters they hold lets you sequence safely around them.</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">Anticipate</t>
   </si>
   <si>
-    <t xml:space="preserve">When your opponent casts a spell, draw 1 card.</t>
+    <t xml:space="preserve">When your opponent casts a spell, draw 1 card and deal 1 damage to them.</t>
   </si>
   <si>
     <t xml:space="preserve">You saw it coming. A Reaction that stops nothing — it simply converts the opponent's tempo into your card advantage.</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">Add 2 HP to a Ward you control. If you control no Ward, create one with 1 HP instead.</t>
+    <t xml:space="preserve">Add 2 HP to a Ward you control. If you control no Ward, create one with 1 HP instead. Then remove 1 Burn marker from yourself.</t>
   </si>
   <si>
     <t xml:space="preserve">Good early-game Ward sustain. Rewards players who already established a Ward on a prior turn.</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">Omen</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at the top 4 cards of your Resource Deck. Put one Material (M) component from among them into your hand and the rest on the bottom in any order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A focused dig that rewards a Material-dense deck. Finds the symbol you need while burying what you don't.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, deal 3 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The L1 starter doom - gives the prophecy identity a presence in rounds 1-4 before the L2+ dooms unlock (m12 finding). One more than Foretell's sting because it arrives two turns late.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-013</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">Foreclosure</t>
   </si>
   <si>
-    <t xml:space="preserve">Your opponent puts the top 2 cards of their Resource Deck into their discard pile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accelerates the opponent’s exhaustion clock — every milled card brings their next reshuffle (and its escalating damage) closer.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, deal 4 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prophecy workhorse - a 4-damage doom on a 2-turn fuse. Announced pressure the opponent must plan around.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-021</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">Far Sight</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at the top 3 cards of your opponent's Resource Deck. You may put one of them into their discard pile. Deal 1 damage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information and light mill in one. Strips an answer off the top before they ever see it.</t>
+    <t xml:space="preserve">Look at the top 3 cards of your Resource Deck and put them back in any order. Prophecy - at the start of your opponent's next turn, deal 2 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scry and doom in one - sculpts your next draws while a short-fuse prophecy lands next turn.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-024</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">Shuffle your discard pile into your Resource Deck, then draw 2 cards.</t>
   </si>
   <si>
-    <t xml:space="preserve">A free reshuffle — resets your deck WITHOUT the exhaustion damage a forced recycle costs, then draws 2. Anti-mill and anti-exhaustion tech.</t>
+    <t xml:space="preserve">A free reshuffle - resets your deck WITHOUT the exhaustion damage a forced recycle costs, then draws 2. Anti-exhaustion tech.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-029</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">Entropy</t>
   </si>
   <si>
-    <t xml:space="preserve">Your opponent puts the top 4 cards of their Resource Deck into their discard pile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mill plan's mid-game accelerant. Four cards a cast adds up fast against a slow deck that wants the game to go long.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's third turn from now, deal 7 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mid-game doom - 7 damage on a 3-turn fuse; cast early and every one of their turns becomes a countdown.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-033</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">Oblivion</t>
   </si>
   <si>
-    <t xml:space="preserve">Your opponent shuffles their hand into their Resource Deck, then puts the top 8 cards of their Resource Deck into their discard pile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mill haymaker — dumps 8 cards toward the opponent’s next exhaustion tick and scrambles their hand on the way.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's third turn from now, deal 9 damage to them. This damage cannot be prevented or absorbed by Wards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prophecy haymaker - 9 unwardable damage in 3 turns. Answer it at cast time or race it.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-044</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">Shuffle your discard pile into your Resource Deck.</t>
   </si>
   <si>
-    <t xml:space="preserve">Counter — Divination (mill / exhaustion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-mill / anti-exhaustion tech — a free recycle that dodges the escalating reshuffle damage. Dead against a fast clock.</t>
+    <t xml:space="preserve">Counter - Divination (prophecy / exhaustion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-exhaustion tech - a free recycle that dodges the escalating reshuffle damage. Dead against a fast clock.</t>
   </si>
   <si>
     <t xml:space="preserve">GAM-017</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">Saboteur's Kit</t>
   </si>
   <si>
-    <t xml:space="preserve">Your opponent puts the top 3 cards of their Resource Deck into their discard pile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counter / Complement — Mill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free mill for any deck — pushes the opponent toward their next exhaustion tick, or pressures a fragile combo deck. Modest at 3 cards and one-per-turn.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, deal 2 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complement - Prophecy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A free time-bomb for any deck - 2 damage on a 2-turn fuse. Modest alone; stacked copies build a schedule of dooms.</t>
   </si>
   <si>
     <t xml:space="preserve">GAM-020</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">Omen</t>
   </si>
   <si>
-    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, deal 3 damage to them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The L1 starter doom - gives the prophecy identity a presence in rounds 1-4 before the L2+ dooms unlock (m12 finding). One more than Foretell's sting because it arrives two turns late.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, deal 2 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The L1 starter doom - gives the prophecy identity a presence in rounds 1-4 before the L2+ dooms unlock (m12 finding). Restored to 2-in-2 (m3 finding): at 3 the guaranteed clock outpaced Abjuration's entire wall economy.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-013</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">Overclock</t>
   </si>
   <si>
-    <t xml:space="preserve">This turn, you may cast 1 additional spell, provided you have a free spell slot and its components are already attached.</t>
+    <t xml:space="preserve">Take 2 damage. This turn, you may cast 1 additional spell, provided you have a free spell slot and its components are already attached.</t>
   </si>
   <si>
     <t xml:space="preserve">Complement — Combo / aggro</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">Stone Stance</t>
   </si>
   <si>
-    <t xml:space="preserve">Until the end of the round, the first Reaction you play costs 1 fewer S component (minimum 1).</t>
+    <t xml:space="preserve">Until the end of the round, spell damage dealt to you is reduced by 1.</t>
   </si>
   <si>
     <t xml:space="preserve">Enables early Reaction spam by discounting the first one. Strong opener for a reactive game plan.</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">Searing Word</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 2 damage. Your opponent discards 1 random component card from their hand.</t>
+    <t xml:space="preserve">Deal 1 damage. Your opponent discards 1 random component card from their hand.</t>
   </si>
   <si>
     <t xml:space="preserve">EVO-005</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">Add 2 HP to a Ward you control. If you control no Ward, create one with 1 HP instead. Then remove 1 Burn marker from yourself.</t>
+    <t xml:space="preserve">Add 2 HP to a Ward you control. If you control no Ward, create one with 2 HP instead. Then remove 1 Burn marker from yourself.</t>
   </si>
   <si>
     <t xml:space="preserve">Good early-game Ward sustain. Rewards players who already established a Ward on a prior turn.</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">Stone Stance</t>
   </si>
   <si>
-    <t xml:space="preserve">Until the end of the round, spell damage dealt to you is reduced by 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enables early Reaction spam by discounting the first one. Strong opener for a reactive game plan.</t>
+    <t xml:space="preserve">Until the end of the round, spell damage dealt to you is reduced by 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round-long -2 to incoming spell damage - the anti-cantrip tax. Charges Reckoning while it blunts aggro; near-irrelevant against big single hits.</t>
   </si>
   <si>
     <t xml:space="preserve">ABJ-006</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">Reckoning</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal damage to your opponent equal to the total amount of damage you have prevented this round.</t>
+    <t xml:space="preserve">Deal damage to your opponent equal to half the total damage you have prevented this match, rounded up. Damage your Wards absorb counts as prevented.</t>
   </si>
   <si>
     <t xml:space="preserve">Rewards a patient defensive game — the more attacks you've weathered and mitigated, the harder this hits. Pairs naturally with Absorb and other prevention effects to set up a large burst in the same round.</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">Foresight</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at the top 3 cards of your Resource Deck. Put one into your hand and the rest back on top in any order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selection over raw draw. Smooths your next two turns and stacks the top of your deck for Premonition or Calculated Draw.</t>
+    <t xml:space="preserve">Look at the top 3 cards of your Resource Deck. Put one into your hand and the rest back on top in any order. Until the end of the round, spell damage dealt to you is reduced by 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selection plus the foreseen-blow flinch - a round-long -1 against chip damage. The seer's early answer to cantrip aggro.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-003</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">Divine</t>
   </si>
   <si>
-    <t xml:space="preserve">Look at the top 2 cards of your Resource Deck. Put one into your hand and the other on the bottom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap filtering. Trades a little card economy for the guarantee that you keep the piece you actually need.</t>
+    <t xml:space="preserve">Look at the top 2 cards of your Resource Deck. Put one into your hand and the other on the bottom. Then remove 1 Burn marker from yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap filtering that also shrugs off a Burn you saw coming. The rider is a pure Evocation tax - dead by design against burn-less schools.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-004</t>
@@ -3469,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>145</v>
@@ -5507,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>435</v>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">DIV-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Scry Glyph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Look at the top card of each player's Resource Deck. You may put either one on the bottom of its owner's deck.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information plus light disruption. Seeing — and pruning — the opponent's next draw is quietly powerful in a long grind.</t>
+    <t xml:space="preserve">Cut the Thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the component cards in your opponent's hand. Choose one; they discard it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Targeted fuel denial - the seer cuts the thread the next turn hangs by. Attached components are safe, so attach-first play dodges it.</t>
   </si>
   <si>
     <t xml:space="preserve">DIV-009</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -2572,7 +2572,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -3828,6 +3828,129 @@
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ABJ-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Warding Tithe</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Abjuration</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Spell</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Spend up to 4 of the damage you have prevented this match. Create a Ward with HP equal to the amount spent.</t>
+        </is>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Ledger family (2026-08-13). Spends the Reckoning bank for tempo - every point spent is a point the late nuke loses. Gives prevention a use against doom decks that never touch wards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ABJ-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Sealed Verdict</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Abjuration</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Spend 6 of the damage you have prevented this match: cancel target spell. Castable only while you have at least 6 prevented.</t>
+        </is>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Ledger family. A cancel funded by the bank instead of scarce attached fuel - the extra answer per round Abjuration lacked against multi-doom turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ABJ-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Restoring Rune</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Abjuration</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Spell</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Spend up to 6 of the damage you have prevented this match. Heal half the amount spent, rounded down.</t>
+        </is>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Ledger family. Sustain option - trades future Reckoning payload for present HP.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">DIV-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reveal the top card of your Resource Deck. If it is a Material (M) component, draw it. Otherwise, put it on the bottom.</t>
+    <t xml:space="preserve">Prophecy of Collapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's second turn from now, destroy their largest Ward.</t>
   </si>
   <si>
     <t xml:space="preserve">Rewards a heavily tuned M deck — the more Material you run, the more often this draws. Quietly punishes greedy multi-school splashes.</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">DIV-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Refocus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return a face-up component attached to one of your prepared spells to your hand.</t>
+    <t xml:space="preserve">Unravel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent's weakest Ward. Look at the top 2 cards of your Resource Deck and put them back in any order.</t>
   </si>
   <si>
     <t xml:space="preserve">Pick a component back up to re-aim it at a different spell. Pure tempo — undoes a misread or frees a piece for a better line.</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">DIV-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Attune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Until the end of the round, the next component you attach to a prepared spell counts as having one additional symbol of a type you choose.</t>
+    <t xml:space="preserve">Flaw in the Weave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your opponent's largest Ward loses half its HP, rounded up.</t>
   </si>
   <si>
     <t xml:space="preserve">The precision fixer: bridges an off-color cost when you're a single symbol short. Embodies the doc's 'right piece at the right time.'</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">Oblivion</t>
   </si>
   <si>
-    <t xml:space="preserve">Prophecy - at the start of your opponent's third turn from now, deal 9 damage to them. This damage cannot be prevented or absorbed by Wards.</t>
+    <t xml:space="preserve">Prophecy - at the start of your opponent's third turn from now, deal 9 damage to them.</t>
   </si>
   <si>
     <t xml:space="preserve">The prophecy haymaker - 9 unwardable damage in 3 turns. Answer it at cast time or race it.</t>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -692,10 +692,10 @@
     <t xml:space="preserve">EVO-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Kindle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Place 1 Burn marker on your opponent.</t>
+    <t xml:space="preserve">Stoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return up to two Verbal-providing component cards from your discard pile to your hand.</t>
   </si>
   <si>
     <t xml:space="preserve">EVO-007</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">VV</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 4 damage to your opponent.</t>
+    <t xml:space="preserve">Deal 5 damage to your opponent.</t>
   </si>
   <si>
     <t xml:space="preserve">EVO-012</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">Fireball</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 5 damage to your opponent.</t>
+    <t xml:space="preserve">Deal 6 damage to your opponent.</t>
   </si>
   <si>
     <t xml:space="preserve">Iconic spell at iconic cost. Anchors the L2 power curve.</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">Mana Burn</t>
   </si>
   <si>
-    <t xml:space="preserve">Cancel target spell that requires a Material (M) component. Deal 2 damage to your opponent.</t>
+    <t xml:space="preserve">Cancel target spell or Reaction that requires a Material (M) component. Deal 2 damage to your opponent.</t>
   </si>
   <si>
     <t xml:space="preserve">The Evocation parallel to Counterbind — same anti-school role but with damage tacked on rather than pure denial.</t>
